--- a/Politics/政治挖掘.xlsx
+++ b/Politics/政治挖掘.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10668" windowHeight="9180"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="20251128" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>漏选A：发展繁荣不应该是靠自己吗？和周边有何关系？</t>
   </si>
@@ -41,6 +41,18 @@
   </si>
   <si>
     <t>漏选B：全球南方只是全球的一部分，国际调解院不止服务于南方</t>
+  </si>
+  <si>
+    <t>没选A：是，但是没有提及“中间道路”</t>
+  </si>
+  <si>
+    <t>错选B:这个回答了中间路线的问题，而且看解析可知，中间路线依然是旧民主主义，和国民党没区别</t>
+  </si>
+  <si>
+    <t>多选1：半殖民地，我看中“殖民地”，对封建社会而言，这个是主要区别</t>
+  </si>
+  <si>
+    <t>漏选2：究竟是看中“半”，还是看中“殖民地”？</t>
   </si>
 </sst>
 </file>
@@ -837,6 +849,174 @@
         <a:xfrm>
           <a:off x="8641080" y="0"/>
           <a:ext cx="3611880" cy="5501640"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>441960</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="5486400"/>
+          <a:ext cx="3528060" cy="5219700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>586740</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="图片 5"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="10789920"/>
+          <a:ext cx="3672840" cy="3108960"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>396240</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="图片 6"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4320540" y="5486400"/>
+          <a:ext cx="3482340" cy="6019800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>556260</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="图片 7"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId8" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8023860" y="6035040"/>
+          <a:ext cx="3642360" cy="5440680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1102,7 +1282,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A28:O32"/>
+  <dimension ref="A28:O79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="28" spans="1:15">
@@ -1121,6 +1301,26 @@
     <row r="32" spans="1:15">
       <c r="O32" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="8:8">
+      <c r="H64" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="H65" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Politics/政治挖掘.xlsx
+++ b/Politics/政治挖掘.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>漏选A：发展繁荣不应该是靠自己吗？和周边有何关系？</t>
   </si>
@@ -53,6 +53,30 @@
   </si>
   <si>
     <t>漏选2：究竟是看中“半”，还是看中“殖民地”？</t>
+  </si>
+  <si>
+    <t>没选A：最后一句话强调中国国情，而不是社会主义</t>
+  </si>
+  <si>
+    <t>错选C：不确定是不是全部，但至少和中国特色强相关了</t>
+  </si>
+  <si>
+    <t>C：我记得平均利润是同一个行业不同企业间平均的</t>
+  </si>
+  <si>
+    <t>D：这里定义的部门难道不是行业的意思？不同行业会均摊利润？</t>
+  </si>
+  <si>
+    <t>漏选D：珠是要素，链是整体，可是串珠没有改变要素啊</t>
+  </si>
+  <si>
+    <t>错选A：多个珠子在一起是量变，形成链就是质变</t>
+  </si>
+  <si>
+    <t>没选A：四个阶段到最后才有货币，怎么能说是固定的呢</t>
+  </si>
+  <si>
+    <t>多选D：记不得两个分别是对应什么了，乱选</t>
   </si>
 </sst>
 </file>
@@ -1029,6 +1053,342 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>487680</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="图片 8"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId9" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4320540" y="12070080"/>
+          <a:ext cx="3573780" cy="5775960"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>563880</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="图片 9"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId10" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8023860" y="12070080"/>
+          <a:ext cx="3649980" cy="4846320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>502285</xdr:colOff>
+      <xdr:row>111</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="图片 10"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId11" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="14630400"/>
+          <a:ext cx="3588385" cy="5829300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="图片 11"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId12" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3703320" y="17922240"/>
+          <a:ext cx="3581400" cy="3139440"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>502920</xdr:colOff>
+      <xdr:row>122</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="图片 12"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId13" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8023860" y="17739360"/>
+          <a:ext cx="3589020" cy="4632960"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>388620</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="图片 13"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId14" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11727180" y="17739360"/>
+          <a:ext cx="3474720" cy="1935480"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>142</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="图片 14"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId15" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="21031200"/>
+          <a:ext cx="3581400" cy="5044440"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>128</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="图片 15"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId16" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3703320" y="21214080"/>
+          <a:ext cx="3619500" cy="2209800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1282,7 +1642,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A28:O79"/>
+  <dimension ref="A28:T131"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="28" spans="1:15">
@@ -1323,6 +1683,46 @@
         <v>7</v>
       </c>
     </row>
+    <row r="94" spans="14:14">
+      <c r="N94" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="14:14">
+      <c r="N95" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="109" spans="20:20">
+      <c r="T109" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110" spans="20:20">
+      <c r="T110" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="130" spans="7:7">
+      <c r="G130" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="131" spans="7:7">
+      <c r="G131" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Politics/政治挖掘.xlsx
+++ b/Politics/政治挖掘.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="20251128" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="20251129" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>漏选A：发展繁荣不应该是靠自己吗？和周边有何关系？</t>
   </si>
@@ -77,6 +77,30 @@
   </si>
   <si>
     <t>多选D：记不得两个分别是对应什么了，乱选</t>
+  </si>
+  <si>
+    <t>排除A：制度建设不是目的，而是手段</t>
+  </si>
+  <si>
+    <t>排除BD：B和D差不多，这题单选，不可能同时选BD</t>
+  </si>
+  <si>
+    <t>排除3：之后就开始社会动荡了（大跃进、文革）</t>
+  </si>
+  <si>
+    <t>排除4：这个是改革开放后形成的</t>
+  </si>
+  <si>
+    <t>排除2：那时改造完按道理是要共产，公有大幅强化</t>
+  </si>
+  <si>
+    <t>2和3：虽然感觉2和3都有错，但3更明显些</t>
+  </si>
+  <si>
+    <t>选A：1935年的何梅协定和华北危急都是A的体现</t>
+  </si>
+  <si>
+    <t>不选C：1931年甚至更早之前鬼子就开始侵华了</t>
   </si>
 </sst>
 </file>
@@ -1392,6 +1416,263 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>525780</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="3611880" cy="5448300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3703320" y="0"/>
+          <a:ext cx="3619500" cy="6797040"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>434340</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7406640" y="0"/>
+          <a:ext cx="3520440" cy="3741420"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="图片 4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11109960" y="0"/>
+          <a:ext cx="3619500" cy="3314700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>480060</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="图片 5"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7406640" y="4023360"/>
+          <a:ext cx="3566160" cy="4739640"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>548640</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="图片 6"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11109960" y="4023360"/>
+          <a:ext cx="3634740" cy="4328160"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
@@ -1734,12 +2015,54 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
+  <dimension ref="A20:S48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <sheetData>
+    <row r="20" spans="1:19">
+      <c r="S20" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
+      <c r="S21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19">
+      <c r="A31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19">
+      <c r="A32" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
+      <c r="A33" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19">
+      <c r="A34" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19">
+      <c r="S47" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19">
+      <c r="S48" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
